--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:009.8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,22 +533,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.2</t>
+          <t>00:020.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>167.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>105.4</t>
+          <t>203.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41020</t>
+          <t>278011</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.1</t>
+          <t>00:029.9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>202.9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1</t>
+          <t>206.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>113666</t>
+          <t>628702</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.2</t>
+          <t>00:039.9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.7</t>
+          <t>97.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>116.2</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>204374</t>
+          <t>752689</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.0</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>108.7</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>278644</t>
+          <t>859815</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,17 +761,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.8</t>
+          <t>00:059.9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>120.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>167.8</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>340788</t>
+          <t>1036684</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.9</t>
+          <t>01:010.2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>118.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>107.3</t>
+          <t>180.8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>388426</t>
+          <t>1212078</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.9</t>
+          <t>01:020.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>117.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>388395</t>
+          <t>1292236</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.2</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>94.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>397539</t>
+          <t>1346476</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.1</t>
+          <t>01:040.2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>422395</t>
+          <t>1393116</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:050.2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>450993</t>
+          <t>1464144</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:060.0</t>
+          <t>01:059.8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>470701</t>
+          <t>1534778</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.9</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>487667</t>
+          <t>1579513</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.7</t>
+          <t>02:019.9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>63.2</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>504368</t>
+          <t>1643202</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.1</t>
+          <t>02:030.0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>528261</t>
+          <t>1705515</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.8</t>
+          <t>02:039.9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>61.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>540129</t>
+          <t>1721944</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.9</t>
+          <t>02:049.7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>528174</t>
+          <t>1702429</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.4</t>
+          <t>02:054.8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>522031</t>
+          <t>1692036</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,63 +1494,6 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>521640</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>

--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.8</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.0</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:020.6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>167.1</t>
+          <t>344.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>203.3</t>
+          <t>442.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>77.34</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>278011</t>
+          <t>598153</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:029.9</t>
+          <t>00:030.7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>202.9</t>
+          <t>442.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>206.6</t>
+          <t>399.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,17 +620,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>628702</t>
+          <t>1418130</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.2</t>
+          <t>306.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>131.8</t>
+          <t>294.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>752689</t>
+          <t>1983389</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.1</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>216.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>286.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>5.84</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>859815</t>
+          <t>2365990</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.9</t>
+          <t>00:059.7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>120.6</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>167.8</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1036684</t>
+          <t>2473137</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>118.6</t>
+          <t>176.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>180.8</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>10.70</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1212078</t>
+          <t>2750450</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.0</t>
+          <t>01:020.2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>167.6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>117.9</t>
+          <t>222.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1292236</t>
+          <t>3018543</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.0</t>
+          <t>01:029.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>235.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>94.1</t>
+          <t>355.8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1346476</t>
+          <t>3418903</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.2</t>
+          <t>01:040.3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>277.7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>357.3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1393116</t>
+          <t>3897996</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.2</t>
+          <t>01:050.1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>174.7</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1464144</t>
+          <t>4111031</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.8</t>
+          <t>02:000.1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>109.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1534778</t>
+          <t>4263660</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.0</t>
+          <t>02:009.9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>135.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.43</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1579513</t>
+          <t>4377861</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.9</t>
+          <t>02:020.0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>220.6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>13.46</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1643202</t>
+          <t>4742321</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:030.5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>285.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>320.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1705515</t>
+          <t>5247684</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.9</t>
+          <t>02:040.0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>124.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>61.4</t>
+          <t>233.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1721944</t>
+          <t>5427013</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.7</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1702429</t>
+          <t>5419188</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,12 +1445,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:054.8</t>
+          <t>02:054.9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1460,22 +1460,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1692036</t>
+          <t>5410048</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
